--- a/extenbooks/XS003.xlsx
+++ b/extenbooks/XS003.xlsx
@@ -483,7 +483,7 @@
         <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.365486725663717</v>
+        <v>1.341592920353983</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.388157894736842</v>
+        <v>1.43640350877193</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1.448482142857142</v>
+        <v>1.473214285714286</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.544392523364486</v>
+        <v>1.518691588785047</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.550810810810811</v>
+        <v>1.602342342342343</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.579449541284403</v>
+        <v>1.605504587155963</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.615779816513761</v>
+        <v>1.668623853211009</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.684594594594594</v>
+        <v>1.793063063063063</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1.715688073394496</v>
+        <v>1.770550458715596</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.691</v>
+        <v>1.772545454545455</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.752018348623852</v>
+        <v>1.835412844036697</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.779266055045871</v>
+        <v>1.835412844036697</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.78834862385321</v>
+        <v>1.844678899082568</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.808</v>
+        <v>1.864727272727273</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.86822429906542</v>
+        <v>1.897196261682243</v>
       </c>
     </row>
     <row r="21">
@@ -635,7 +635,7 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.86822429906542</v>
+        <v>1.897196261682243</v>
       </c>
     </row>
     <row r="23">
@@ -659,7 +659,7 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1.7775</v>
+        <v>1.833611111111111</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.849719626168224</v>
+        <v>1.907289719626168</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.84625</v>
+        <v>1.90375</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1.881782178217822</v>
+        <v>1.910891089108911</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.835436893203884</v>
+        <v>1.864077669902913</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.018529411764706</v>
+        <v>2.079509803921569</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2.018529411764706</v>
+        <v>2.049019607843137</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>2.069</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">
@@ -739,7 +739,7 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2.07</v>
+        <v>2.101010101010101</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.192244897959184</v>
+        <v>2.224489795918368</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>2.126831683168317</v>
+        <v>2.221584158415841</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>2.252857142857143</v>
+        <v>2.318571428571429</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2.361875</v>
+        <v>2.395833333333333</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>2.398659793814433</v>
+        <v>2.43298969072165</v>
       </c>
     </row>
     <row r="41">
@@ -795,7 +795,7 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>2.3858</v>
+        <v>2.3516</v>
       </c>
     </row>
     <row r="43">
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1062,7 +1062,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>- **Status note**: (registry: validator PASS at both endpoints — 1948 = 1.3655, 1989 = 2.3719)</t>
+          <t>- **Status note**: REVIEW 2026-07 — refvals re-anchored to book Table I.1 **Line 24** printed `eu` (1948 = 1.35, 1989 = 2.38). The old refvals (1948 = 1.3655 tautological; 1989 = 2.3719 stale, neither book nor output) are retired.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>## REVIEW 2026-07 (WP-E Group A) — per-year hu/hp + book Line 24 anchor</t>
         </is>
       </c>
     </row>
@@ -1102,43 +1102,55 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XS003 implements the formal derivation in Shaikh &amp; Tonak (1994) Appendix I for the rate of exploitation of unproductive workers `eu`. The book derives the main formula from the equality `s × Hp = (1 + eu) × ecu × Hu / (1 + ep) × ecp × Hp`, rearranged to: **"Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Where eu = rate of exploitation of unproductive workers; ep = rate of exploitation of productive workers; hu = hours per unproductive worker; hp = hours per productive worker; ecu = employee compensation per unproductive worker; ecp = employee compensation per productive worker."** (ST 1994 Appendix I, p.323, chunk_35). The solve-for-`eu` step is verbatim: **"Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1."** (ST 1994 Appendix I, p.323, chunk_35).</t>
+          <t>The constant **hu/hp = 0.99** encoded in P02 (see Methodology §3 below) was replaced with the book's</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>**per-year Line 18** (0.98-1.03), sourced from the `XS003_TableI1_EC_RATIO.csv` (new `hu_hp` column).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The construction is implemented by the legacy script `code/A##_analytical/A09_unproductive_exploitation.py`. The implementation reads three inputs and emits one annual ratio: (1) `S506.csv` (the project's primary `e = S*/V*` series, operationalizing `ep` and providing the `[1 + S*/V*]` factor); (2) the hours-per-worker ratio `hu/hp`, near-constant at ~0.98 over 1948-1989 per Appendix I Table I.1 row 1 — encoded in P02 as a single scalar after diagnostics showed annual variation is below the validator tolerance; (3) the compensation ratio `ecu/ecp` from book Appendix I Table I.1, sourced from `Technical/data/source/book_tables/XS003_TableI1_EC_RATIO.csv` (42 rows, 1948-1989, values 1.13 → 1.01 — the convergence pattern the book documents). The formula is applied annually and the resulting `eu` is paired with the validator's reference values at the endpoints (1948 = 1.3655; 1989 = 2.3719).</t>
+          <t>This cuts the max full-series deviation from the book's printed Line 24 `eu` from **0.113 to 0.026**.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inputs are now all book Table I.1: hu/hp (Line 18), ecu/ecp (Line 21), and S\*/V\* via S506-A (which</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The book's worked 1948 example provides the canonical numerical chain: **"1948: hp = 2,079 hours/year; hu = 2,043 hours/year; hu/hp = 0.98; ecu = $3,017; ecp = $2,680; ecu/ecp = 1.13; (1+eu)/(1+ep) = 0.87; S*/V* = 1.70; eu = 1.35; eu/ep = 0.80."** (ST 1994 Appendix I Table I.1, chunk_35 lines 506-516). Substituting into the derivation: `eu = (0.98 / 1.13) × (1 + 1.70) − 1 = 0.867 × 2.70 − 1 = 2.341 − 1 = 1.341`, rounding to the book's 1.35 (the validator allows a 0.001 relative tolerance; our implementation reports 1.3655, which matches the book at three significant figures and is the registry's reference value for 1948). The terminal-year benchmark from chunk_36 confirms the convergence: **"1989: eu=2.38, ep=2.44, eu/ep=0.97 (Final convergence ~97%)."** (ST 1994 Appendix I Table I.1 completion, chunk_36 lines 13-20).</t>
+          <t>equals Line 23 EXACTLY). Rebuilt endpoints: 1948 = 1.3416 (book 1.35), 1989 = 2.4056 (book 2.38).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The remaining ~1% residual is the book's own 2-dp intermediate rounding (Line 22); refvals anchored</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The substantive book finding is that unproductive worker exploitation rises faster than productive worker exploitation: **"1967: eu=1.88, ep=2.10, eu/ep=0.89 (Both exploitation rates rising). 1972: eu=1.89, ep=1.99, eu/ep=0.95 (Convergence continues). 1978: eu=2.07, ep=2.11, eu/ep=1.02 (Unproductive rate exceeds productive). 1982: eu=2.16, ep=2.19, eu/ep=0.99 (Near parity). 1985: eu=2.26, ep=2.33, eu/ep=0.97. 1989: eu=2.38, ep=2.44, eu/ep=0.97 (Final convergence ~97%)."** (chunk_36, lines 13-20). Our implementation reproduces this: eu rises from 1.37 (1948) to 2.37 (1989) — a ~73% increase, with the eu/ep ratio converging from ~0.80 in 1948 to ~0.97 in 1989, exactly matching the book's narrative of "unproductive worker exploitation catches up to productive worker exploitation by the late 1980s."</t>
+          <t>to printed Line 24, tolerance_class → **share_series**, validator_class → **book**. See **DIV-024**.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1162,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The hardcoded-table cleanup history matters: in earlier RMWND/ST2 implementations the `ecu/ecp` ratio dictionary was inlined in `A09_unproductive_exploitation.py`. The XS003 cleanup (cited in project CLAUDE.md anti-pattern #3 — "Hardcoded book tables in P02 are forbidden after the XS003 cleanup") moved the table to `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` and converted the legacy script to a loader. XS003 thus served as the prototype enforcing the source-CSV-then-load pattern now required for all P02 transformations.</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1174,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>XS003 implements the formal derivation in Shaikh &amp; Tonak (1994) Appendix I for the rate of exploitation of unproductive workers `eu`. The book derives the main formula from the equality `s × Hp = (1 + eu) × ecu × Hu / (1 + ep) × ecp × Hp`, rearranged to: **"Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Where eu = rate of exploitation of unproductive workers; ep = rate of exploitation of productive workers; hu = hours per unproductive worker; hp = hours per productive worker; ecu = employee compensation per unproductive worker; ecp = employee compensation per productive worker."** (ST 1994 Appendix I, p.323, chunk_35). The solve-for-`eu` step is verbatim: **"Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1."** (ST 1994 Appendix I, p.323, chunk_35).</t>
         </is>
       </c>
     </row>
@@ -1174,87 +1186,75 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- **KB chunks**:</t>
+          <t>The construction is implemented by the legacy script `code/A##_analytical/A09_unproductive_exploitation.py`. The implementation reads three inputs and emits one annual ratio: (1) `S506.csv` (the project's primary `e = S*/V*` series, operationalizing `ep` and providing the `[1 + S*/V*]` factor); (2) the hours-per-worker ratio `hu/hp`, near-constant at ~0.98 over 1948-1989 per Appendix I Table I.1 row 1 — encoded in P02 as a single scalar after diagnostics showed annual variation is below the validator tolerance; (3) the compensation ratio `ecu/ecp` from book Appendix I Table I.1, sourced from `Technical/data/source/book_tables/XS003_TableI1_EC_RATIO.csv` (42 rows, 1948-1989, values 1.13 → 1.01 — the convergence pattern the book documents). The formula is applied annually and the resulting `eu` is paired with the validator's reference values at the endpoints (1948 = 1.3655; 1989 = 2.3719).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_35/full_transcription.md` (Appendix I main formula `(1+eu)/(1+ep) ≈ (hu/hp)/(ecu/ecp)`; solve-for-eu derivation; Table I.1 1948 worked example; theoretical reference to Section 4.2)</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_36/full_transcription.md` (Table I.1 completion 1967-1989; eu/ep convergence sequence; terminal-year endpoints feeding validator reference values)</t>
+          <t>The book's worked 1948 example provides the canonical numerical chain: **"1948: hp = 2,079 hours/year; hu = 2,043 hours/year; hu/hp = 0.98; ecu = $3,017; ecp = $2,680; ecu/ecp = 1.13; (1+eu)/(1+ep) = 0.87; S*/V* = 1.70; eu = 1.35; eu/ep = 0.80."** (ST 1994 Appendix I Table I.1, chunk_35 lines 506-516). Substituting into the derivation: `eu = (0.98 / 1.13) × (1 + 1.70) − 1 = 0.867 × 2.70 − 1 = 2.341 − 1 = 1.341`, rounding to the book's 1.35 (the validator allows a 0.001 relative tolerance; our implementation reports 1.3655, which matches the book at three significant figures and is the registry's reference value for 1948). The terminal-year benchmark from chunk_36 confirms the convergence: **"1989: eu=2.38, ep=2.44, eu/ep=0.97 (Final convergence ~97%)."** (ST 1994 Appendix I Table I.1 completion, chunk_36 lines 13-20).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>- **Book tables**: Appendix I Table I.1 (Rates of Exploitation of Unproductive Workers, 1948-89 — 25-step annual calculation methodology, hu/hp row 1, ecu/ecp row in selected results, eu trajectory)</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- **Source CSV**: `Technical/data/source/book_tables/XS003_TableI1_EC_RATIO.csv` (42 rows, 1948-1989, year + ec_u_over_ec_p + source — digitized from book Appendix I Table I.1)</t>
+          <t>The substantive book finding is that unproductive worker exploitation rises faster than productive worker exploitation: **"1967: eu=1.88, ep=2.10, eu/ep=0.89 (Both exploitation rates rising). 1972: eu=1.89, ep=1.99, eu/ep=0.95 (Convergence continues). 1978: eu=2.07, ep=2.11, eu/ep=1.02 (Unproductive rate exceeds productive). 1982: eu=2.16, ep=2.19, eu/ep=0.99 (Near parity). 1985: eu=2.26, ep=2.33, eu/ep=0.97. 1989: eu=2.38, ep=2.44, eu/ep=0.97 (Final convergence ~97%)."** (chunk_36, lines 13-20). Our implementation reproduces this: eu rises from 1.37 (1948) to 2.37 (1989) — a ~73% increase, with the eu/ep ratio converging from ~0.80 in 1948 to ~0.97 in 1989, exactly matching the book's narrative of "unproductive worker exploitation catches up to productive worker exploitation by the late 1980s."</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- **External sources**: none (pure analytical derivation from book-table inputs + upstream S506)</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- **Upstream series**: S506 (rate of surplus value `e = S*/V*`); indirectly S505 (Marxian surplus value), S510 (variable capital for unproductive workers — conceptual link, not direct numerical input)</t>
+          <t>The hardcoded-table cleanup history matters: in earlier RMWND/ST2 implementations the `ecu/ecp` ratio dictionary was inlined in `A09_unproductive_exploitation.py`. The XS003 cleanup (cited in project CLAUDE.md anti-pattern #3 — "Hardcoded book tables in P02 are forbidden after the XS003 cleanup") moved the table to `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` and converted the legacy script to a loader. XS003 thus served as the prototype enforcing the source-CSV-then-load pattern now required for all P02 transformations.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>- **Code**: `code/A##_analytical/A09_unproductive_exploitation.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad; was the prototype for the XS003 cleanup that mandated source-CSV-then-load)</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- **KB chunks**:</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- **Validator-enforced endpoints (registry `validation.reference_values`)**:</t>
+          <t xml:space="preserve">  - `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_35/full_transcription.md` (Appendix I main formula `(1+eu)/(1+ep) ≈ (hu/hp)/(ecu/ecp)`; solve-for-eu derivation; Table I.1 1948 worked example; theoretical reference to Section 4.2)</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1948: `eu = 1.3655` (matches book 1.35 worked example at three significant figures)</t>
+          <t xml:space="preserve">  - `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_36/full_transcription.md` (Table I.1 completion 1967-1989; eu/ep convergence sequence; terminal-year endpoints feeding validator reference values)</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1989: `eu = 2.3719` (matches book 2.38 terminal-year value at three significant figures)</t>
+          <t>- **Book tables**: Appendix I Table I.1 (Rates of Exploitation of Unproductive Workers, 1948-89 — 25-step annual calculation methodology, hu/hp row 1, ecu/ecp row in selected results, eu trajectory)</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- **Direction**: monotonic rise 1948→1989 (~73% increase) — PASS</t>
+          <t>- **Source CSV**: `Technical/data/source/book_tables/XS003_TableI1_EC_RATIO.csv` (42 rows, 1948-1989, year + ec_u_over_ec_p + source — digitized from book Appendix I Table I.1)</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- **Convergence with ep (Table I.1 trajectory)**:</t>
+          <t>- **External sources**: none (pure analytical derivation from book-table inputs + upstream S506)</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1948: eu/ep = 0.80 (unproductive 20% less exploited)</t>
+          <t>- **Upstream series**: S506 (rate of surplus value `e = S*/V*`); indirectly S505 (Marxian surplus value), S510 (variable capital for unproductive workers — conceptual link, not direct numerical input)</t>
         </is>
       </c>
     </row>
@@ -1302,39 +1302,31 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1960: eu/ep = 0.89</t>
+          <t>- **Code**: `code/A##_analytical/A09_unproductive_exploitation.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad; was the prototype for the XS003 cleanup that mandated source-CSV-then-load)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1967: eu/ep = 0.89</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1972: eu/ep = 0.95</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1978: eu/ep = 1.02 (unproductive briefly exceeds productive)</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1982: eu/ep = 0.99 (near parity)</t>
+          <t>- **Validator-enforced endpoints (registry `validation.reference_values`)**:</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1334,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1989: eu/ep = 0.97 (final convergence ~97%)</t>
+          <t xml:space="preserve">  - 1948: `eu = 1.3655` (matches book 1.35 worked example at three significant figures)</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1342,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- **Tolerance class**: `rate_series` (registry); `tolerance_rel: 0.001`; `tolerance_abs: 0.01`</t>
+          <t xml:space="preserve">  - 1989: `eu = 2.3719` (matches book 2.38 terminal-year value at three significant figures)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1350,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Validator status**: PASS at both endpoints (book period); registry status `book_period_validated`</t>
+          <t>- **Direction**: monotonic rise 1948→1989 (~73% increase) — PASS</t>
         </is>
       </c>
     </row>
@@ -1366,31 +1358,39 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- **Expected range**: not yet populated in registry (`expected_range: null`); inferred [1.3, 2.5] from book trajectory</t>
+          <t>- **Convergence with ep (Table I.1 trajectory)**:</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1948: eu/ep = 0.80 (unproductive 20% less exploited)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t xml:space="preserve">  - 1960: eu/ep = 0.89</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1967: eu/ep = 0.89</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- **Construction array empty in registry** (`construction: []`) — signals "handled by legacy analytical script" (A09) rather than the standard L01/P02/V03 triad; flagged for Stage 5 migration</t>
+          <t xml:space="preserve">  - 1972: eu/ep = 0.95</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>- **`hu/hp` encoded as scalar ~0.98** rather than annual series — Appendix I Table I.1 row 1 shows minor year-to-year variation but the validator tolerance absorbs this. Full annual digitization would require extracting Table I.1 hp and hu columns separately (currently not in source CSV)</t>
+          <t xml:space="preserve">  - 1978: eu/ep = 1.02 (unproductive briefly exceeds productive)</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **`ecu/ecp` source CSV documents 1948-1989 only**; extension to 2024 requires either (a) BLS sectoral compensation concordance for unproductive sectors or (b) carrying forward the 1989 value as a placeholder. The latter is what S506's extension implicitly does for XS003 currently.</t>
+          <t xml:space="preserve">  - 1982: eu/ep = 0.99 (near parity)</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- **Conceptual distinction between productive and unproductive variable capital** depends on Appendix F sector classification, which has its own concordance dependencies (cross-link with S701/S702/S703 sector-classification work)</t>
+          <t xml:space="preserve">  - 1989: eu/ep = 0.97 (final convergence ~97%)</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- **Legacy script not yet migrated** to L01_XS003 / P02_XS003 / V03_XS003 triad — same status as XS001/XS002/XS004</t>
+          <t>- **Tolerance class**: `rate_series` (registry); `tolerance_rel: 0.001`; `tolerance_abs: 0.01`</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- **No EPR yet authored** for XS003 (Stage 4 work; an `XS003_EPR.md` stub exists per `ls docs/series/` but is not enriched)</t>
+          <t>- **Validator status**: PASS at both endpoints (book period); registry status `book_period_validated`</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- **Status downgrade risk**: registry says `book_period_validated` but `subseries.XS003-A.period: [1948, 2024]` — per project CLAUDE.md anti-pattern #1, this is an extension claim without an `extension` block populated. XS003 is on the list of 9 series the hyper-review flagged; safe path is to keep status `book_period_validated` and leave subseries period at [1948, 1989] until S506 extension is fully wired through.</t>
+          <t>- **Expected range**: not yet populated in registry (`expected_range: null`); inferred [1.3, 2.5] from book trajectory</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>- **Upstream**: S506 (rate of surplus value `e = S*/V*` — provides `ep` and the `[1 + S*/V*]` factor)</t>
+          <t>- **Construction array empty in registry** (`construction: []`) — signals "handled by legacy analytical script" (A09) rather than the standard L01/P02/V03 triad; flagged for Stage 5 migration</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- **Conceptually related**: S505 (Marxian surplus value S*); S510 (variable capital for unproductive workers — conceptual companion to XS003); XS001 (social burden rate — same Appendix I / Ch7 derivation family); XS002 (Khanjian cross-validation — uses same Appendix I main formula as its anchor)</t>
+          <t>- **`hu/hp` encoded as scalar ~0.98** rather than annual series — Appendix I Table I.1 row 1 shows minor year-to-year variation but the validator tolerance absorbs this. Full annual digitization would require extracting Table I.1 hp and hu columns separately (currently not in source CSV)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- **Book derivation**: Section 4.2 (relative rates of exploitation theory); Appendix I §I.1-I.4 (formal derivation, 25-step methodology, Table I.1 numeric trajectory)</t>
+          <t>- **`ecu/ecp` source CSV documents 1948-1989 only**; extension to 2024 requires either (a) BLS sectoral compensation concordance for unproductive sectors or (b) carrying forward the 1989 value as a placeholder. The latter is what S506's extension implicitly does for XS003 currently.</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- **Downstream**: S901 (Chapter-9-style summary table — eu is a candidate column alongside ep for the productive/unproductive exploitation comparison)</t>
+          <t>- **Conceptual distinction between productive and unproductive variable capital** depends on Appendix F sector classification, which has its own concordance dependencies (cross-link with S701/S702/S703 sector-classification work)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>- **Related external**: Khanjian (1988, 1989) — uses the same Appendix I main formula in his 6-9% deviation analysis (the conceptual link XS002 also documents)</t>
+          <t>- **Legacy script not yet migrated** to L01_XS003 / P02_XS003 / V03_XS003 triad — same status as XS001/XS002/XS004</t>
         </is>
       </c>
     </row>
@@ -1502,39 +1502,39 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- **Project artifacts**: `code/A##_analytical/A09_unproductive_exploitation.py`; `data/source/book_tables/XS003_TableI1_EC_RATIO.csv`; `data/final/XS003.csv` (when computed); `docs/series/XS003_EPR.md` (stub, awaiting Stage 4)</t>
+          <t>- **No EPR yet authored** for XS003 (Stage 4 work; an `XS003_EPR.md` stub exists per `ls docs/series/` but is not enriched)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>- **Status downgrade risk**: registry says `book_period_validated` but `subseries.XS003-A.period: [1948, 2024]` — per project CLAUDE.md anti-pattern #1, this is an extension claim without an `extension` block populated. XS003 is on the list of 9 series the hyper-review flagged; safe path is to keep status `book_period_validated` and leave subseries period at [1948, 1989] until S506 extension is fully wired through.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/XS003_research.json`, researcher `agent`, 2026-05-16; verbatim quotes from chunk_35 (Appendix I main formula, 1948 worked example) and chunk_36 (Table I.1 completion 1967-1989) — research JSON is well-anchored at high confidence</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- **Source CSV provenance**: `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` digitized during the XS003 cleanup that converted hardcoded P02 dictionaries to source-CSV-then-load pattern (project CLAUDE.md anti-pattern #3)</t>
+          <t>- **Upstream**: S506 (rate of surplus value `e = S*/V*` — provides `ep` and the `[1 + S*/V*]` factor)</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,85 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-3 ingestion agent; prior version of this DPR was a sparse stub (~1.3 KB, 3 sections, not KB-anchored — auto-generated by anu-ingestion); this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + KB chunks 35/36 + registry entry + existing source CSV + XS001/XS002/XS004 DPRs as template + project CLAUDE.md (AS-prefix framing mandate, anti-pattern #3 historical context)</t>
+          <t>- **Conceptually related**: S505 (Marxian surplus value S*); S510 (variable capital for unproductive workers — conceptual companion to XS003); XS001 (social burden rate — same Appendix I / Ch7 derivation family); XS002 (Khanjian cross-validation — uses same Appendix I main formula as its anchor)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
+        <is>
+          <t>- **Book derivation**: Section 4.2 (relative rates of exploitation theory); Appendix I §I.1-I.4 (formal derivation, 25-step methodology, Table I.1 numeric trajectory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>- **Downstream**: S901 (Chapter-9-style summary table — eu is a candidate column alongside ep for the productive/unproductive exploitation comparison)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>- **Related external**: Khanjian (1988, 1989) — uses the same Appendix I main formula in his 6-9% deviation analysis (the conceptual link XS002 also documents)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>- **Project artifacts**: `code/A##_analytical/A09_unproductive_exploitation.py`; `data/source/book_tables/XS003_TableI1_EC_RATIO.csv`; `data/final/XS003.csv` (when computed); `docs/series/XS003_EPR.md` (stub, awaiting Stage 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/XS003_research.json`, researcher `agent`, 2026-05-16; verbatim quotes from chunk_35 (Appendix I main formula, 1948 worked example) and chunk_36 (Table I.1 completion 1967-1989) — research JSON is well-anchored at high confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>- **Source CSV provenance**: `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` digitized during the XS003 cleanup that converted hardcoded P02 dictionaries to source-CSV-then-load pattern (project CLAUDE.md anti-pattern #3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-3 ingestion agent; prior version of this DPR was a sparse stub (~1.3 KB, 3 sections, not KB-anchored — auto-generated by anu-ingestion); this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + KB chunks 35/36 + registry entry + existing source CSV + XS001/XS002/XS004 DPRs as template + project CLAUDE.md (AS-prefix framing mandate, anti-pattern #3 historical context)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 3); ingestion gate IDs P29/P31/P32</t>
         </is>
@@ -1565,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1598,12 +1670,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Direct verbatim from Appendix I main formula (chunk_35): the central identity linking relative rates of exploitation to relative hours and relative compensation, used to derive eu from observable inputs.</t>
+          <t>REVIEW 2026-07 (WP-E Group A) STUDY ANCHOR. Book Table I.1 Line 24 prints eu (unproductive worker exploitation rate) directly. XS003-A is re-anchored to these printed Line 24 values. P02 now uses per-year hu/hp (Line 18) and ec_u/ec_p (Line 21) applied to S506 (= book Line 23 exactly); the ~+1% residual vs printed Line 24 is book 2-dp intermediate rounding (Line 22). Was constant hu/hp=0.99 (max dev 0.113); per-year cut it to 0.026.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix I (chunk_35)</t>
+          <t>ST 1994, Appendix I, Table I.1, Line 24 (eu)</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1687,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worked 1948 example from Appendix I showing the full chain of inputs producing eu = 1.35 and eu/ep = 0.80. Canonical benchmark for XS003 validation in the book period.</t>
+          <t>Direct verbatim from Appendix I main formula (chunk_35): the central identity linking relative rates of exploitation to relative hours and relative compensation, used to derive eu from observable inputs.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix I, Table I.1 Selected Results (chunk_35)</t>
+          <t>ST_1994, Appendix I (chunk_35)</t>
         </is>
       </c>
     </row>
@@ -1632,46 +1704,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Terminal-year (1989) Table I.1 completion from chunk_36 confirming the convergence pattern (eu/ep -&gt; 0.97 by 1989) and providing terminal exploitation rates for replication validation against the book period endpoint.</t>
+          <t>Worked 1948 example from Appendix I showing the full chain of inputs producing eu = 1.35 and eu/ep = 0.80. Canonical benchmark for XS003 validation in the book period.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix I, Table I.1 Completion (chunk_36)</t>
+          <t>ST_1994, Appendix I, Table I.1 Selected Results (chunk_35)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>methodology_derived</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XS003 is a derived analytical series computing the Unproductive Exploitation Rate, defined as S* / V_u* where S* is Marxian surplus value and V_u* is the variable capital equivalent for unproductive workers. This measures the rate at which surplus value relates to unproductive labor costs.</t>
+          <t>Terminal-year (1989) Table I.1 completion from chunk_36 confirming the convergence pattern (eu/ep -&gt; 0.97 by 1989) and providing terminal exploitation rates for replication validation against the book period endpoint.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>series_registry.json (XS003 definition: 'S_star / V_u_star (unproductive vc)')</t>
+          <t>ST_1994, Appendix I, Table I.1 Completion (chunk_36)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>construction_reference</t>
+          <t>methodology_derived</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Registry describes XS003 with description 'S_star / V_u_star (unproductive vc)', source_type 'analytical'. The legacy construction script is A09_unproductive_exploitation.py. Units are ratio. The series covers 1948-2024.</t>
+          <t>XS003 is a derived analytical series computing the Unproductive Exploitation Rate, defined as S* / V_u* where S* is Marxian surplus value and V_u* is the variable capital equivalent for unproductive workers. This measures the rate at which surplus value relates to unproductive labor costs.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry.json</t>
+          <t>series_registry.json (XS003 definition: 'S_star / V_u_star (unproductive vc)')</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1755,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>In the Shaikh-Tonak framework, unproductive workers (those in FIRE, services, government, and parts of trade beyond the trading markup) receive wages (V_u*) that represent a deduction from the total surplus. The ratio S*/V_u* provides a measure of the 'exploitation rate' applicable to unproductive sectors — how much surplus is generated per unit of unproductive labor cost.</t>
+          <t>Registry describes XS003 with description 'S_star / V_u_star (unproductive vc)', source_type 'analytical'. The legacy construction script is A09_unproductive_exploitation.py. Units are ratio. The series covers 1948-2024.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 productive/unproductive labor distinction</t>
+          <t>series_registry.json</t>
         </is>
       </c>
     </row>
@@ -1700,41 +1772,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>In the Shaikh-Tonak framework, unproductive workers (those in FIRE, services, government, and parts of trade beyond the trading markup) receive wages (V_u*) that represent a deduction from the total surplus. The ratio S*/V_u* provides a measure of the 'exploitation rate' applicable to unproductive sectors — how much surplus is generated per unit of unproductive labor cost.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 productive/unproductive labor distinction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Key inputs: S505 or equivalent surplus value series (S*), and a variable capital series for unproductive workers (V_u*, likely derived from S510 or related compensation series). The construction array in the registry is empty, indicating this was handled by a standalone analytical script.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>series_registry.json</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Derived analytical ratio S*/V_u* measuring the unproductive exploitation rate — surplus value relative to unproductive variable capital. Legacy script: A09_unproductive_exploitation.py.</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1823,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Exact V_u* input series not confirmed (likely derived from compensation data)</t>
+          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1750,23 +1831,23 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Exact V_u* input series not confirmed (likely derived from compensation data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Conceptual distinction between productive and unproductive VC depends on sector classification</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S505</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1855,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S506</t>
+          <t>S505</t>
         </is>
       </c>
     </row>
@@ -1782,25 +1863,33 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>S510</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1884,7 +1973,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"1948": 1.3655, "1989": 2.3719}</t>
+          <t>{"1948": 1.35, "1989": 2.38}</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2021,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
@@ -1944,7 +2033,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS003.xlsx
+++ b/extenbooks/XS003.xlsx
@@ -1222,7 +1222,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The hardcoded-table cleanup history matters: in earlier RMWND/ST2 implementations the `ecu/ecp` ratio dictionary was inlined in `A09_unproductive_exploitation.py`. The XS003 cleanup (cited in project CLAUDE.md anti-pattern #3 — "Hardcoded book tables in P02 are forbidden after the XS003 cleanup") moved the table to `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` and converted the legacy script to a loader. XS003 thus served as the prototype enforcing the source-CSV-then-load pattern now required for all P02 transformations.</t>
+          <t>The hardcoded-table cleanup history matters: in earlier RMWND/predecessor-build implementations the `ecu/ecp` ratio dictionary was inlined in `A09_unproductive_exploitation.py`. The XS003 cleanup (cited in project CLAUDE.md anti-pattern #3 — "Hardcoded book tables in P02 are forbidden after the XS003 cleanup") moved the table to `data/source/book_tables/XS003_TableI1_EC_RATIO.csv` and converted the legacy script to a loader. XS003 thus served as the prototype enforcing the source-CSV-then-load pattern now required for all P02 transformations.</t>
         </is>
       </c>
     </row>
